--- a/sheets/대금율보/검수/아미새.xlsx
+++ b/sheets/대금율보/검수/아미새.xlsx
@@ -2799,7 +2799,7 @@
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕
-淋㳞‹</t>
+淋㳞</t>
         </is>
       </c>
       <c r="E4" s="23" t="inlineStr">
@@ -2848,7 +2848,7 @@
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋潕
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
@@ -2929,7 +2929,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢㳞‹
+          <t xml:space="preserve">潢㳞
 –
 h</t>
         </is>
@@ -2955,7 +2955,7 @@
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㳞
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 –
 ㄱ</t>
         </is>
@@ -3099,7 +3099,7 @@
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲林
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無‹
+          <t xml:space="preserve">無
 –潢</t>
         </is>
       </c>
@@ -3195,7 +3195,7 @@
       <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-△潢‹</t>
+△潢</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 –㳞</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/아미새.xlsx
+++ b/sheets/대금율보/검수/아미새.xlsx
@@ -2727,20 +2727,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="108.11" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="96.77" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="96.77" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -2821,7 +2821,7 @@
       <c r="H4" s="21"/>
       <c r="I4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="96.77" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
       <c r="H5" s="21"/>
       <c r="I5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="96.77" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
       <c r="H6" s="21"/>
       <c r="I6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="96.77" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="96.77" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="25" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="96.77" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="96.77" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="96.77" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="96.77" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="96.77" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="96.77" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -3175,7 +3175,7 @@
       <c r="H14" s="21"/>
       <c r="I14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="96.77" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -3204,7 +3204,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="96.77" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="96.77" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -3270,7 +3270,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="96.77" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="24"/>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="96.77" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="96.77" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="23"/>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="96.77" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="96.77" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -3428,6 +3428,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="37"/>
 </worksheet>
 </file>